--- a/johorup-system/data/students_real.xlsx
+++ b/johorup-system/data/students_real.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JohorUP\JohorUP\johorup-system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DE79C31-5BB0-4C3E-82E2-A83A259AE48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B8FD7D-40CE-4B45-BEB1-BF013CED7380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
